--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,122 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,8 +854,14 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,8 +937,14 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1020,14 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1055,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>5000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>6200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>6500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>6000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>4800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>5700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>5500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>3300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>4500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>3400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1217,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1261,8 +1300,14 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,85 +1415,93 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F17" s="3">
         <v>9000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>9200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>8100</v>
       </c>
       <c r="O17" s="3">
         <v>9200</v>
       </c>
       <c r="P17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="R17" s="3">
         <v>7200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>7400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1450,76 +1509,82 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-8100</v>
       </c>
       <c r="O18" s="3">
         <v>-9200</v>
       </c>
       <c r="P18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-7400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-8600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-6800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,22 +1623,22 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G20" s="3">
         <v>1400</v>
       </c>
       <c r="H20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1580,14 +1647,14 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1595,37 +1662,43 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1633,76 +1706,82 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-7000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-6200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-6900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-9500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-9200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-7400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-8500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-6500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-7400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-7300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-4800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-6000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1710,16 +1789,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
@@ -1743,19 +1822,19 @@
         <v>300</v>
       </c>
       <c r="P22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1767,96 +1846,108 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-8500</v>
       </c>
       <c r="L23" s="3">
         <v>-7300</v>
       </c>
       <c r="M23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-7400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-7400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-7400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-8500</v>
       </c>
       <c r="L26" s="3">
         <v>-7300</v>
       </c>
       <c r="M26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O26" s="3">
         <v>-9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-8400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-8500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-7400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-6000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-8500</v>
       </c>
       <c r="L27" s="3">
         <v>-7300</v>
       </c>
       <c r="M27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O27" s="3">
         <v>-9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-8500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-7400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-6200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2480,22 +2619,22 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-1400</v>
+        <v>-1100</v>
       </c>
       <c r="F32" s="3">
-        <v>-1400</v>
+        <v>-1300</v>
       </c>
       <c r="G32" s="3">
         <v>-1400</v>
       </c>
       <c r="H32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2504,14 +2643,14 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2519,114 +2658,126 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-8500</v>
       </c>
       <c r="L33" s="3">
         <v>-7300</v>
       </c>
       <c r="M33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O33" s="3">
         <v>-9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-6700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-6200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-8500</v>
       </c>
       <c r="L35" s="3">
         <v>-7300</v>
       </c>
       <c r="M35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O35" s="3">
         <v>-9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-6700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-6200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,112 +3090,120 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F41" s="3">
         <v>26000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>66600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>24700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>29100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>29300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>36400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>41600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>45000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>53300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>44200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>52600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>57300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>63500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>71400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>12900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>13500</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F42" s="3">
         <v>62900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>80400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>99600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>107900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>59000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>53200</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3037,11 +3216,11 @@
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3073,85 +3252,97 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
       <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
         <v>600</v>
-      </c>
-      <c r="T43" s="3">
-        <v>200</v>
-      </c>
-      <c r="U43" s="3">
-        <v>300</v>
       </c>
       <c r="V43" s="3">
         <v>200</v>
       </c>
       <c r="W43" s="3">
+        <v>300</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3227,162 +3418,180 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F45" s="3">
         <v>4000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
       </c>
       <c r="H45" s="3">
         <v>1300</v>
       </c>
       <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>3000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>87500</v>
+      </c>
+      <c r="F46" s="3">
         <v>94000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>99200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>114200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>122600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>127300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>79900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>38000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>30700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>38500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>42200</v>
-      </c>
-      <c r="O46" s="3">
-        <v>46300</v>
-      </c>
-      <c r="P46" s="3">
-        <v>55200</v>
       </c>
       <c r="Q46" s="3">
         <v>46300</v>
       </c>
       <c r="R46" s="3">
+        <v>55200</v>
+      </c>
+      <c r="S46" s="3">
+        <v>46300</v>
+      </c>
+      <c r="T46" s="3">
         <v>53800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>59600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>65500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>74600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>15200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3401,15 +3610,15 @@
       <c r="H47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>1000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3422,11 +3631,11 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3458,52 +3667,58 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>100</v>
+      </c>
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
       <c r="P48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
@@ -3512,31 +3727,37 @@
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V48" s="3">
         <v>500</v>
       </c>
       <c r="W48" s="3">
+        <v>500</v>
+      </c>
+      <c r="X48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y48" s="3">
         <v>100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3775,50 +4014,50 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
@@ -3826,25 +4065,31 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>89400</v>
+      </c>
+      <c r="F54" s="3">
         <v>95900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>101000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>116200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>123000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>128400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>81400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>38500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>39100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>42900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>47100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>55900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>47000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>54200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>60000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>66000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>75100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>17200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>10500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>15400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,85 +4314,93 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>2700</v>
       </c>
       <c r="V57" s="3">
         <v>500</v>
       </c>
       <c r="W57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4144,38 +4411,38 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+      <c r="H58" s="3">
         <v>7600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7000</v>
       </c>
       <c r="I58" s="3">
         <v>7000</v>
       </c>
       <c r="J58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L58" s="3">
         <v>7100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4188,11 +4455,11 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4209,210 +4476,228 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>3600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>5000</v>
       </c>
       <c r="S59" s="3">
         <v>3600</v>
       </c>
       <c r="T59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="U59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V59" s="3">
         <v>4500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>13400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>15400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>12700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>7100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3">
+        <v>100</v>
+      </c>
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>13700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>14200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>14000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4426,39 +4711,45 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>1100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F62" s="3">
         <v>1100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4470,10 +4761,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -4482,43 +4773,49 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
       </c>
       <c r="S62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>300</v>
       </c>
       <c r="V62" s="3">
+        <v>300</v>
+      </c>
+      <c r="W62" s="3">
+        <v>300</v>
+      </c>
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F66" s="3">
         <v>6300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>15600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>18500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>20900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>19900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>21400</v>
-      </c>
-      <c r="L66" s="3">
-        <v>20200</v>
       </c>
       <c r="M66" s="3">
         <v>21400</v>
       </c>
       <c r="N66" s="3">
+        <v>20200</v>
+      </c>
+      <c r="O66" s="3">
+        <v>21400</v>
+      </c>
+      <c r="P66" s="3">
         <v>19200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>19800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>7400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5068,25 +5403,31 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>128200</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>115700</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>114400</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-250000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-239100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-231300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-223600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-216500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-210100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-204600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-196300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-188200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-180900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-172400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-165100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-155300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-147000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-137500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-130100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-122700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-114200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-107700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-100300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-115500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-109500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-102300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>82500</v>
+      </c>
+      <c r="F76" s="3">
         <v>89600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>95100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>101700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>107500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>109900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>60500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>17100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>23700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>35600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>40000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>46800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>54500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>60700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>67700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-115500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-109500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-102300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-8100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-8500</v>
       </c>
       <c r="L81" s="3">
         <v>-7300</v>
       </c>
       <c r="M81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="O81" s="3">
         <v>-9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-6700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-6200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,8 +6286,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-9900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-8600</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-7100</v>
       </c>
       <c r="K89" s="3">
         <v>-6200</v>
       </c>
       <c r="L89" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-7600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-8900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-8400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-7700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-4100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-4700</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-5600</v>
       </c>
       <c r="Z89" s="3">
         <v>-4000</v>
       </c>
       <c r="AA89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6392,17 +6833,17 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -6412,29 +6853,29 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -6443,22 +6884,28 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,49 +7064,55 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F94" s="3">
         <v>18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>19600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>9000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-48300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4900</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -6674,22 +7133,28 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7510,97 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-7700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>55300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>56000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>13700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>4100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>16100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>63500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>9800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>10500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F102" s="3">
         <v>12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-54000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>41900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>9100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-8500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-6200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-7900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>58400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>5700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>6500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -860,8 +864,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,8 +950,11 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E12" s="3">
         <v>8800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,91 +1443,95 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E17" s="3">
         <v>11900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1509,82 +1539,85 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,13 +1657,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1400</v>
       </c>
       <c r="H20" s="3">
         <v>1400</v>
@@ -1638,26 +1672,26 @@
         <v>1400</v>
       </c>
       <c r="J20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1668,37 +1702,40 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>200</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-500</v>
       </c>
       <c r="AA20" s="3">
         <v>-500</v>
       </c>
       <c r="AB20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1706,82 +1743,85 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1795,13 +1835,13 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
@@ -1828,16 +1868,16 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1852,102 +1892,108 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
       </c>
       <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-7400</v>
       </c>
       <c r="S23" s="3">
         <v>-7400</v>
       </c>
       <c r="T23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U23" s="3">
         <v>-8500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-7400</v>
       </c>
       <c r="W23" s="3">
         <v>-7400</v>
       </c>
       <c r="X23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-7400</v>
       </c>
       <c r="S26" s="3">
         <v>-7400</v>
       </c>
       <c r="T26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U26" s="3">
         <v>-8500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-7400</v>
       </c>
       <c r="S27" s="3">
         <v>-7400</v>
       </c>
       <c r="T27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U27" s="3">
         <v>-8500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,13 +2689,13 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
       </c>
       <c r="H32" s="3">
         <v>-1400</v>
@@ -2634,26 +2704,26 @@
         <v>-1400</v>
       </c>
       <c r="J32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2664,120 +2734,126 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>500</v>
       </c>
       <c r="AA32" s="3">
         <v>500</v>
       </c>
       <c r="AB32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-7400</v>
       </c>
       <c r="S33" s="3">
         <v>-7400</v>
       </c>
       <c r="T33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U33" s="3">
         <v>-8500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-7400</v>
       </c>
       <c r="S35" s="3">
         <v>-7400</v>
       </c>
       <c r="T35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U35" s="3">
         <v>-8500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,121 +3178,125 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>53300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>63500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E42" s="3">
         <v>59000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>62900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>80400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>107900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>53200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3222,8 +3312,8 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3258,43 +3348,46 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1000</v>
       </c>
       <c r="F43" s="3">
         <v>1000</v>
       </c>
       <c r="G43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H43" s="3">
         <v>2100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>400</v>
       </c>
       <c r="K43" s="3">
         <v>400</v>
       </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
+      <c r="N43" s="3">
+        <v>200</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
@@ -3302,11 +3395,11 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>300</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
@@ -3315,34 +3408,37 @@
         <v>100</v>
       </c>
       <c r="U43" s="3">
+        <v>100</v>
+      </c>
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>300</v>
-      </c>
-      <c r="X43" s="3">
-        <v>200</v>
       </c>
       <c r="Y43" s="3">
         <v>200</v>
       </c>
       <c r="Z43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,204 +3520,213 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E46" s="3">
         <v>76800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>94000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>99200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>114200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>122600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>127300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>79900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>55200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>53800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>65500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>74600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3637,8 +3742,8 @@
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3673,31 +3778,34 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1600</v>
       </c>
       <c r="F48" s="3">
         <v>1600</v>
       </c>
       <c r="G48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -3706,13 +3814,13 @@
         <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -3721,7 +3829,7 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
@@ -3733,7 +3841,7 @@
         <v>400</v>
       </c>
       <c r="V48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>500</v>
@@ -3742,13 +3850,13 @@
         <v>500</v>
       </c>
       <c r="Y48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
+      <c r="AA48" s="3">
+        <v>100</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4020,46 +4140,46 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
         <v>900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>400</v>
+      </c>
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
       <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3">
         <v>500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>300</v>
       </c>
       <c r="T52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4071,25 +4191,28 @@
         <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E54" s="3">
         <v>78600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>89400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>123000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>128400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>81400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>39100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>75100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,91 +4446,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4417,10 +4551,10 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
+        <v>100</v>
+      </c>
+      <c r="I58" s="3">
         <v>7600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>7000</v>
       </c>
       <c r="J58" s="3">
         <v>7000</v>
@@ -4429,23 +4563,23 @@
         <v>7000</v>
       </c>
       <c r="L58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M58" s="3">
         <v>7100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4461,8 +4595,8 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4482,174 +4616,183 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>3400</v>
       </c>
       <c r="O59" s="3">
         <v>3400</v>
       </c>
       <c r="P59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1900</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4660,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
@@ -4669,38 +4812,38 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
+        <v>100</v>
+      </c>
+      <c r="J61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4717,22 +4860,25 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4740,10 +4886,10 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
       </c>
       <c r="G62" s="3">
         <v>1100</v>
@@ -4752,7 +4898,7 @@
         <v>1100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -4767,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -4779,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>200</v>
@@ -4788,7 +4934,7 @@
         <v>200</v>
       </c>
       <c r="U62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V62" s="3">
         <v>300</v>
@@ -4797,16 +4943,16 @@
         <v>300</v>
       </c>
       <c r="X62" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y62" s="3">
         <v>800</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>500</v>
       </c>
       <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
+      <c r="AA62" s="3">
+        <v>500</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5409,25 +5577,28 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>128200</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>115700</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>114400</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-262400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-250000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-239100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-231300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-223600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-216500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-210100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-204600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-196300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-188200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-180900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-172400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-165100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-155300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-147000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-137500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-130100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-122700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-114200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-107700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-115500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-109500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E76" s="3">
         <v>72300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>82500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>95100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>101700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>107500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>109900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>60500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>40000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>54500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>60700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>67700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-115500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-109500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-7400</v>
       </c>
       <c r="S81" s="3">
         <v>-7400</v>
       </c>
       <c r="T81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="U81" s="3">
         <v>-8500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6839,13 +7060,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6859,26 +7080,26 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -6890,22 +7111,25 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,52 +7297,55 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>19600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-48300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7139,22 +7369,25 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,59 +7759,62 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>55300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>16100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -7576,31 +7822,34 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>63500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>10500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-54000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>41900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>58400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,156 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -867,8 +871,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,8 +960,11 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1049,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,94 +1084,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E12" s="3">
         <v>10000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,31 +1260,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1329,8 +1349,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E17" s="3">
         <v>13300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-14100</v>
       </c>
       <c r="E18" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,53 +1681,54 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1300</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1705,123 +1739,129 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
       </c>
       <c r="W20" s="3">
+        <v>200</v>
+      </c>
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-500</v>
       </c>
       <c r="AB20" s="3">
         <v>-500</v>
       </c>
       <c r="AC20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-14100</v>
       </c>
       <c r="E21" s="3">
-        <v>-10900</v>
+        <v>-13300</v>
       </c>
       <c r="F21" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-7800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="N21" s="3">
         <v>-7000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1838,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
@@ -1871,16 +1911,16 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
+        <v>300</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1895,105 +1935,111 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>200</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
       <c r="AD22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-7400</v>
       </c>
       <c r="T23" s="3">
         <v>-7400</v>
       </c>
       <c r="U23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V23" s="3">
         <v>-8500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-7400</v>
       </c>
       <c r="X23" s="3">
         <v>-7400</v>
       </c>
       <c r="Y23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-7400</v>
       </c>
       <c r="T26" s="3">
         <v>-7400</v>
       </c>
       <c r="U26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V26" s="3">
         <v>-8500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-7400</v>
       </c>
       <c r="T27" s="3">
         <v>-7400</v>
       </c>
       <c r="U27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V27" s="3">
         <v>-8500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,53 +2747,56 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1300</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2737,123 +2807,129 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
       </c>
       <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>500</v>
       </c>
       <c r="AB32" s="3">
         <v>500</v>
       </c>
       <c r="AC32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-7400</v>
       </c>
       <c r="T33" s="3">
         <v>-7400</v>
       </c>
       <c r="U33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V33" s="3">
         <v>-8500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-7400</v>
       </c>
       <c r="T35" s="3">
         <v>-7400</v>
       </c>
       <c r="U35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V35" s="3">
         <v>-8500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,127 +3265,131 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>57300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>63500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13500</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E42" s="3">
         <v>56500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>59000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>62900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>80400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>107900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3315,8 +3405,8 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3351,46 +3441,49 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>800</v>
-      </c>
-      <c r="E43" s="3">
-        <v>700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>1300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>400</v>
       </c>
       <c r="L43" s="3">
         <v>400</v>
       </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
+      <c r="O43" s="3">
+        <v>200</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
@@ -3398,11 +3491,11 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" s="3">
         <v>300</v>
-      </c>
-      <c r="S43" s="3">
-        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
@@ -3411,57 +3504,60 @@
         <v>100</v>
       </c>
       <c r="V43" s="3">
+        <v>100</v>
+      </c>
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>300</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>200</v>
       </c>
       <c r="Z43" s="3">
         <v>200</v>
       </c>
       <c r="AA43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3523,213 +3619,222 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>800</v>
+      </c>
+      <c r="F45" s="3">
+        <v>700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K45" s="3">
+        <v>800</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>600</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="Y45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="Z45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
-        <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="X45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E46" s="3">
         <v>72100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>76800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>94000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>99200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>114200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>122600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>79900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>38500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>46300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>53800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>59600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>65500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>74600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3745,8 +3850,8 @@
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3781,34 +3886,37 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1600</v>
       </c>
       <c r="G48" s="3">
         <v>1600</v>
       </c>
       <c r="H48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>100</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
@@ -3817,13 +3925,13 @@
         <v>100</v>
       </c>
       <c r="N48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
@@ -3832,7 +3940,7 @@
         <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>400</v>
@@ -3844,7 +3952,7 @@
         <v>400</v>
       </c>
       <c r="W48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X48" s="3">
         <v>500</v>
@@ -3853,13 +3961,13 @@
         <v>500</v>
       </c>
       <c r="Z48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
+      <c r="AB48" s="3">
+        <v>100</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>4</v>
@@ -3867,8 +3975,11 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4242,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4143,46 +4263,46 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
       </c>
       <c r="K52" s="3">
+        <v>200</v>
+      </c>
+      <c r="L52" s="3">
         <v>900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
       </c>
       <c r="N52" s="3">
+        <v>400</v>
+      </c>
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
       </c>
       <c r="R52" s="3">
+        <v>400</v>
+      </c>
+      <c r="S52" s="3">
         <v>500</v>
-      </c>
-      <c r="S52" s="3">
-        <v>300</v>
       </c>
       <c r="T52" s="3">
         <v>300</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4194,25 +4314,28 @@
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E54" s="3">
         <v>73800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>78600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>89400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>81400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>54200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>75100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,117 +4577,121 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>7600</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3">
-        <v>7000</v>
+        <v>7700</v>
       </c>
       <c r="K58" s="3">
         <v>7000</v>
@@ -4566,23 +4700,23 @@
         <v>7000</v>
       </c>
       <c r="M58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N58" s="3">
         <v>7100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4598,8 +4732,8 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4619,234 +4753,243 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>5100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O59" s="3">
         <v>3900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>3900</v>
-      </c>
-      <c r="O59" s="3">
-        <v>3400</v>
       </c>
       <c r="P59" s="3">
         <v>3400</v>
       </c>
       <c r="Q59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R59" s="3">
         <v>4000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4863,45 +5006,48 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>1100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4916,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -4928,7 +5074,7 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>200</v>
@@ -4937,7 +5083,7 @@
         <v>200</v>
       </c>
       <c r="V62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W62" s="3">
         <v>300</v>
@@ -4946,16 +5092,16 @@
         <v>300</v>
       </c>
       <c r="Y62" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z62" s="3">
         <v>800</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>500</v>
       </c>
       <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
+      <c r="AB62" s="3">
+        <v>500</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5580,25 +5748,28 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>128200</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>115700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>114400</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-275600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-262400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-250000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-239100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-231300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-223600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-216500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-210100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-204600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-196300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-188200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-180900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-172400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-165100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-155300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-147000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-137500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-130100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-122700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-114200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-107700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-115500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E76" s="3">
         <v>66200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>82500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>95100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>107500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>60500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>27300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>54500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>67700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-115500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-7400</v>
       </c>
       <c r="T81" s="3">
         <v>-7400</v>
       </c>
       <c r="U81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="V81" s="3">
         <v>-8500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6606,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7262,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7053,8 +7274,8 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -7063,13 +7284,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7083,26 +7304,26 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7114,22 +7335,25 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,55 +7527,58 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E94" s="3">
         <v>2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -7372,22 +7602,25 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,62 +8005,65 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>55300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>16100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -7825,54 +8071,57 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>63500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>10500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,90 +8183,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-54000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>41900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>58400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,137 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,8 +814,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -874,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E12" s="3">
         <v>11200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1277,8 +1296,8 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>400</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -1286,12 +1305,12 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1352,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1697,41 +1730,41 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1742,126 +1775,132 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
       </c>
       <c r="X20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-500</v>
       </c>
       <c r="AC20" s="3">
         <v>-500</v>
       </c>
       <c r="AD20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8500</v>
       </c>
       <c r="H21" s="3">
         <v>-8900</v>
       </c>
       <c r="I21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-8200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1881,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
       </c>
       <c r="K22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
@@ -1914,16 +1953,16 @@
         <v>300</v>
       </c>
       <c r="T22" s="3">
+        <v>300</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1938,108 +1977,114 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>200</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
       </c>
       <c r="AE22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-7400</v>
       </c>
       <c r="U23" s="3">
         <v>-7400</v>
       </c>
       <c r="V23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W23" s="3">
         <v>-8500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y23" s="3">
         <v>-7400</v>
       </c>
       <c r="Z23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2127,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-7400</v>
       </c>
       <c r="U26" s="3">
         <v>-7400</v>
       </c>
       <c r="V26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W26" s="3">
         <v>-8500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-7400</v>
       </c>
       <c r="U27" s="3">
         <v>-7400</v>
       </c>
       <c r="V27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W27" s="3">
         <v>-8500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2765,41 +2834,41 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2810,126 +2879,132 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
       </c>
       <c r="X32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>500</v>
       </c>
       <c r="AC32" s="3">
         <v>500</v>
       </c>
       <c r="AD32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-7400</v>
       </c>
       <c r="U33" s="3">
         <v>-7400</v>
       </c>
       <c r="V33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W33" s="3">
         <v>-8500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-7400</v>
       </c>
       <c r="U35" s="3">
         <v>-7400</v>
       </c>
       <c r="V35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W35" s="3">
         <v>-8500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,133 +3351,137 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>52600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>57300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>63500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13500</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E42" s="3">
         <v>49400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>56500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>59000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>62900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>80400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>107900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>53200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3408,8 +3497,8 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3444,25 +3533,28 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>500</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
@@ -3470,23 +3562,23 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>1300</v>
-      </c>
-      <c r="L43" s="3">
-        <v>400</v>
       </c>
       <c r="M43" s="3">
         <v>400</v>
       </c>
       <c r="N43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
+      <c r="P43" s="3">
+        <v>200</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
@@ -3494,11 +3586,11 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
-      </c>
-      <c r="T43" s="3">
-        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
@@ -3507,34 +3599,37 @@
         <v>100</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>300</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>200</v>
       </c>
       <c r="AB43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3559,8 +3654,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3622,186 +3717,195 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>500</v>
+      </c>
+      <c r="P45" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="U45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="W45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
-        <v>800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="X45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E46" s="3">
         <v>67300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>72100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>76800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>87500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>94000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>99200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>114200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>79900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>55200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>53800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>59600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>65500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>74600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3826,18 +3930,18 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3853,8 +3957,8 @@
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3889,37 +3993,40 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1600</v>
       </c>
       <c r="H48" s="3">
         <v>1600</v>
       </c>
       <c r="I48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>100</v>
@@ -3928,13 +4035,13 @@
         <v>100</v>
       </c>
       <c r="O48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
       </c>
       <c r="Q48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
@@ -3943,7 +4050,7 @@
         <v>300</v>
       </c>
       <c r="T48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
@@ -3955,7 +4062,7 @@
         <v>400</v>
       </c>
       <c r="X48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y48" s="3">
         <v>500</v>
@@ -3964,13 +4071,13 @@
         <v>500</v>
       </c>
       <c r="AA48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB48" s="3">
         <v>100</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
+      <c r="AC48" s="3">
+        <v>100</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>4</v>
@@ -3978,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,13 +4361,16 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -4266,46 +4385,46 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
       </c>
       <c r="L52" s="3">
+        <v>200</v>
+      </c>
+      <c r="M52" s="3">
         <v>900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
       </c>
       <c r="O52" s="3">
+        <v>400</v>
+      </c>
+      <c r="P52" s="3">
         <v>300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
       </c>
       <c r="S52" s="3">
+        <v>400</v>
+      </c>
+      <c r="T52" s="3">
         <v>500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>300</v>
       </c>
       <c r="U52" s="3">
         <v>300</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4317,25 +4436,28 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E54" s="3">
         <v>68900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>89400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>95900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>101000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>123000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>128400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>81400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>55900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>54200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>75100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,97 +4707,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4691,10 +4824,10 @@
         <v>300</v>
       </c>
       <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
         <v>7700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>7000</v>
       </c>
       <c r="L58" s="3">
         <v>7000</v>
@@ -4703,23 +4836,23 @@
         <v>7000</v>
       </c>
       <c r="N58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O58" s="3">
         <v>7100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4735,8 +4868,8 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4756,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4782,217 +4918,223 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3900</v>
-      </c>
-      <c r="P59" s="3">
-        <v>3400</v>
       </c>
       <c r="Q59" s="3">
         <v>3400</v>
       </c>
       <c r="R59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E60" s="3">
         <v>9100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1900</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>700</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>900</v>
       </c>
       <c r="F61" s="3">
         <v>900</v>
       </c>
       <c r="G61" s="3">
+        <v>900</v>
+      </c>
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5009,22 +5151,25 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5049,8 +5194,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5065,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -5077,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -5086,7 +5231,7 @@
         <v>200</v>
       </c>
       <c r="W62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X62" s="3">
         <v>300</v>
@@ -5095,16 +5240,16 @@
         <v>300</v>
       </c>
       <c r="Z62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA62" s="3">
         <v>800</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>500</v>
       </c>
       <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3">
+        <v>500</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5751,25 +5918,28 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>128200</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>115700</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>114400</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-287000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-275600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-262400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-250000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-239100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-231300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-223600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-216500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-210100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-204600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-196300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-188200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-180900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-172400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-165100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-155300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-147000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-137500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-130100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-122700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-114200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-107700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-115500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E76" s="3">
         <v>59000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>66200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>82500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>95100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>101700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>107500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>27300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>40000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>67700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-115500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-7400</v>
       </c>
       <c r="U81" s="3">
         <v>-7400</v>
       </c>
       <c r="V81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="W81" s="3">
         <v>-8500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7150,88 +7366,91 @@
         <v>-9600</v>
       </c>
       <c r="E89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7274,11 +7494,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7287,13 +7507,13 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7307,26 +7527,26 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7338,22 +7558,25 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,58 +7756,61 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E94" s="3">
         <v>7700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-48300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -7605,22 +7834,25 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,8 +7911,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,65 +8250,68 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E100" s="3">
         <v>5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>55300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>56000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>16100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -8074,31 +8319,34 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>63500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>10500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8186,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-54000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>41900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>58400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -817,8 +821,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E12" s="3">
         <v>9300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1308,12 +1328,12 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E17" s="3">
         <v>12200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1736,38 +1770,38 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="K20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1778,134 +1812,140 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
       </c>
       <c r="Y20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-500</v>
       </c>
       <c r="AD20" s="3">
         <v>-500</v>
       </c>
       <c r="AE20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-8900</v>
       </c>
       <c r="I21" s="3">
         <v>-8900</v>
       </c>
       <c r="J21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-8200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1923,13 +1963,13 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
       <c r="L22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
@@ -1956,16 +1996,16 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
+        <v>300</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1980,111 +2020,117 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
       </c>
       <c r="AF22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-7400</v>
       </c>
       <c r="V23" s="3">
         <v>-7400</v>
       </c>
       <c r="W23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X23" s="3">
         <v>-8500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z23" s="3">
         <v>-7400</v>
       </c>
       <c r="AA23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-7400</v>
       </c>
       <c r="V26" s="3">
         <v>-7400</v>
       </c>
       <c r="W26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X26" s="3">
         <v>-8500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-7400</v>
       </c>
       <c r="V27" s="3">
         <v>-7400</v>
       </c>
       <c r="W27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X27" s="3">
         <v>-8500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2840,38 +2910,38 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="K32" s="3">
+        <v>200</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2882,129 +2952,135 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>500</v>
       </c>
       <c r="AD32" s="3">
         <v>500</v>
       </c>
       <c r="AE32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-7400</v>
       </c>
       <c r="V33" s="3">
         <v>-7400</v>
       </c>
       <c r="W33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X33" s="3">
         <v>-8500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-7400</v>
       </c>
       <c r="V35" s="3">
         <v>-7400</v>
       </c>
       <c r="W35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X35" s="3">
         <v>-8500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,139 +3438,143 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E41" s="3">
         <v>34100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>53300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>52600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>57300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>63500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>71400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13500</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E42" s="3">
         <v>73500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>49400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>59000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>62900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>80400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>99600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>107900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>53200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3500,8 +3590,8 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3545,43 +3638,43 @@
         <v>500</v>
       </c>
       <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>1300</v>
-      </c>
-      <c r="M43" s="3">
-        <v>400</v>
       </c>
       <c r="N43" s="3">
         <v>400</v>
       </c>
       <c r="O43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
+      <c r="Q43" s="3">
+        <v>200</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
@@ -3589,11 +3682,11 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3">
         <v>300</v>
-      </c>
-      <c r="U43" s="3">
-        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
@@ -3602,34 +3695,37 @@
         <v>100</v>
       </c>
       <c r="X43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>300</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>200</v>
       </c>
       <c r="AB43" s="3">
         <v>200</v>
       </c>
       <c r="AC43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3657,8 +3753,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3720,192 +3816,201 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E46" s="3">
         <v>109400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>67300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>87500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>99200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>114200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>122600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>79900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>38000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>38500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>55200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>46300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>53800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>59600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>65500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>74600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3933,18 +4038,18 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3960,8 +4065,8 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3996,40 +4101,43 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1600</v>
       </c>
       <c r="I48" s="3">
         <v>1600</v>
       </c>
       <c r="J48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
@@ -4038,13 +4146,13 @@
         <v>100</v>
       </c>
       <c r="P48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
       </c>
       <c r="R48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
@@ -4053,7 +4161,7 @@
         <v>300</v>
       </c>
       <c r="U48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V48" s="3">
         <v>400</v>
@@ -4065,7 +4173,7 @@
         <v>400</v>
       </c>
       <c r="Y48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z48" s="3">
         <v>500</v>
@@ -4074,13 +4182,13 @@
         <v>500</v>
       </c>
       <c r="AB48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AC48" s="3">
         <v>100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
+      <c r="AD48" s="3">
+        <v>100</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4373,7 +4493,7 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -4388,46 +4508,46 @@
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>300</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
         <v>900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>400</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
       </c>
       <c r="P52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>700</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
       </c>
       <c r="T52" s="3">
+        <v>400</v>
+      </c>
+      <c r="U52" s="3">
         <v>500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>300</v>
       </c>
       <c r="V52" s="3">
         <v>300</v>
       </c>
       <c r="W52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4439,25 +4559,28 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E54" s="3">
         <v>110900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>89400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>101000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>116200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>123000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>81400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>55900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>54200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>75100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15400</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4827,10 +4961,10 @@
         <v>300</v>
       </c>
       <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="L58" s="3">
         <v>7700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>7000</v>
       </c>
       <c r="M58" s="3">
         <v>7000</v>
@@ -4839,23 +4973,23 @@
         <v>7000</v>
       </c>
       <c r="O58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P58" s="3">
         <v>7100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>600</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4871,8 +5005,8 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4921,163 +5058,169 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>3500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>3400</v>
       </c>
       <c r="R59" s="3">
         <v>3400</v>
       </c>
       <c r="S59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="3">
         <v>10500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5085,59 +5228,59 @@
         <v>700</v>
       </c>
       <c r="E61" s="3">
+        <v>700</v>
+      </c>
+      <c r="F61" s="3">
         <v>800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>900</v>
       </c>
       <c r="G61" s="3">
         <v>900</v>
       </c>
       <c r="H61" s="3">
+        <v>900</v>
+      </c>
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -5154,22 +5297,25 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>1100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5197,8 +5343,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5213,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -5225,7 +5371,7 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
         <v>200</v>
@@ -5234,7 +5380,7 @@
         <v>200</v>
       </c>
       <c r="X62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y62" s="3">
         <v>300</v>
@@ -5243,16 +5389,16 @@
         <v>300</v>
       </c>
       <c r="AA62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB62" s="3">
         <v>800</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>500</v>
       </c>
       <c r="AC62" s="3">
         <v>500</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
+      <c r="AD62" s="3">
+        <v>500</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E66" s="3">
         <v>11300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3300</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5921,25 +6089,28 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>128200</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>115700</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>114400</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-297400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-287000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-275600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-262400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-250000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-239100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-231300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-223600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-216500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-204600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-196300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-188200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-180900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-172400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-165100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-155300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-147000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-137500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-130100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-122700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-114200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-107700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-100300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E76" s="3">
         <v>99600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>82500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>95100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>101700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>109900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>54500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>67700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-115500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-7400</v>
       </c>
       <c r="V81" s="3">
         <v>-7400</v>
       </c>
       <c r="W81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="X81" s="3">
         <v>-8500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-9600</v>
+        <v>-13500</v>
       </c>
       <c r="E89" s="3">
         <v>-9600</v>
       </c>
       <c r="F89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="G89" s="3">
         <v>-8700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,13 +7703,14 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7497,11 +7718,11 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -7510,13 +7731,13 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7530,26 +7751,26 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -7561,22 +7782,25 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,61 +7986,64 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-48300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -7837,22 +8067,25 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7914,8 +8148,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,68 +8496,71 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E100" s="3">
         <v>51500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>55300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>56000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>16100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -8322,31 +8568,34 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>63500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>10500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8374,8 +8623,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8437,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E102" s="3">
         <v>18000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>41900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>58400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -824,8 +828,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E12" s="3">
         <v>7800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1331,12 +1351,12 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1397,8 +1417,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E17" s="3">
         <v>11500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,38 +1807,38 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1815,140 +1849,146 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-500</v>
       </c>
       <c r="AE20" s="3">
         <v>-500</v>
       </c>
       <c r="AF20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-12200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-8900</v>
       </c>
       <c r="J21" s="3">
         <v>-8900</v>
       </c>
       <c r="K21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="L21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1966,13 +2006,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -1999,16 +2039,16 @@
         <v>300</v>
       </c>
       <c r="V22" s="3">
+        <v>300</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2023,114 +2063,120 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>100</v>
       </c>
       <c r="AF22" s="3">
         <v>100</v>
       </c>
       <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-7400</v>
       </c>
       <c r="W23" s="3">
         <v>-7400</v>
       </c>
       <c r="X23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-7400</v>
       </c>
       <c r="AA23" s="3">
         <v>-7400</v>
       </c>
       <c r="AB23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-7400</v>
       </c>
       <c r="W26" s="3">
         <v>-7400</v>
       </c>
       <c r="X26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-7400</v>
       </c>
       <c r="W27" s="3">
         <v>-7400</v>
       </c>
       <c r="X27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2913,38 +2983,38 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2955,132 +3025,138 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>500</v>
       </c>
       <c r="AE32" s="3">
         <v>500</v>
       </c>
       <c r="AF32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-7400</v>
       </c>
       <c r="W33" s="3">
         <v>-7400</v>
       </c>
       <c r="X33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-7400</v>
       </c>
       <c r="W35" s="3">
         <v>-7400</v>
       </c>
       <c r="X35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,145 +3525,149 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E41" s="3">
         <v>19400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>41600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>44200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>52600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>57300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>63500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>71400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13500</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E42" s="3">
         <v>83900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>49400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>56500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>59000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>50600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>62900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>80400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>99600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>107900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>59000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3593,8 +3683,8 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3629,55 +3719,58 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
       </c>
       <c r="F43" s="3">
+        <v>500</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>1300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>400</v>
       </c>
       <c r="O43" s="3">
         <v>400</v>
       </c>
       <c r="P43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
+      <c r="R43" s="3">
+        <v>200</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
@@ -3685,11 +3778,11 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="3">
         <v>300</v>
-      </c>
-      <c r="V43" s="3">
-        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
@@ -3698,34 +3791,37 @@
         <v>100</v>
       </c>
       <c r="Y43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>300</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>200</v>
       </c>
       <c r="AC43" s="3">
         <v>200</v>
       </c>
       <c r="AD43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE43" s="3">
         <v>100</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3756,8 +3852,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3819,198 +3915,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>207200</v>
+      </c>
+      <c r="E46" s="3">
         <v>105600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>67300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>87500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>94000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>114200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>122600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>127300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>79900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>38500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>42200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>55200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>46300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>53800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>59600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>65500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>74600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4041,18 +4146,18 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4068,8 +4173,8 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4104,43 +4209,46 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1600</v>
       </c>
       <c r="J48" s="3">
         <v>1600</v>
       </c>
       <c r="K48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>100</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
@@ -4149,13 +4257,13 @@
         <v>100</v>
       </c>
       <c r="Q48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
       </c>
       <c r="S48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T48" s="3">
         <v>300</v>
@@ -4164,7 +4272,7 @@
         <v>300</v>
       </c>
       <c r="V48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W48" s="3">
         <v>400</v>
@@ -4176,7 +4284,7 @@
         <v>400</v>
       </c>
       <c r="Z48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA48" s="3">
         <v>500</v>
@@ -4185,13 +4293,13 @@
         <v>500</v>
       </c>
       <c r="AC48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AD48" s="3">
         <v>100</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
+      <c r="AE48" s="3">
+        <v>100</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,19 +4601,22 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -4511,46 +4631,46 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
+        <v>300</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
       <c r="N52" s="3">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3">
         <v>900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
       <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
       </c>
       <c r="U52" s="3">
+        <v>400</v>
+      </c>
+      <c r="V52" s="3">
         <v>500</v>
-      </c>
-      <c r="V52" s="3">
-        <v>300</v>
       </c>
       <c r="W52" s="3">
         <v>300</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4562,25 +4682,28 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208300</v>
+      </c>
+      <c r="E54" s="3">
         <v>107000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>89400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>95900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>101000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>123000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>128400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>81400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>47000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>54200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>75100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +4969,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4964,10 +5098,10 @@
         <v>300</v>
       </c>
       <c r="L58" s="3">
+        <v>300</v>
+      </c>
+      <c r="M58" s="3">
         <v>7700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>7000</v>
       </c>
       <c r="N58" s="3">
         <v>7000</v>
@@ -4976,23 +5110,23 @@
         <v>7000</v>
       </c>
       <c r="P58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>7100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5008,8 +5142,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5029,8 +5163,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5061,229 +5198,235 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3900</v>
-      </c>
-      <c r="R59" s="3">
-        <v>3400</v>
       </c>
       <c r="S59" s="3">
         <v>3400</v>
       </c>
       <c r="T59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>700</v>
       </c>
       <c r="F61" s="3">
+        <v>700</v>
+      </c>
+      <c r="G61" s="3">
         <v>800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>900</v>
       </c>
       <c r="H61" s="3">
         <v>900</v>
       </c>
       <c r="I61" s="3">
+        <v>900</v>
+      </c>
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5300,22 +5443,25 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5346,8 +5492,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5362,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5374,7 +5520,7 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W62" s="3">
         <v>200</v>
@@ -5383,7 +5529,7 @@
         <v>200</v>
       </c>
       <c r="Y62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z62" s="3">
         <v>300</v>
@@ -5392,16 +5538,16 @@
         <v>300</v>
       </c>
       <c r="AB62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC62" s="3">
         <v>800</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>500</v>
       </c>
       <c r="AD62" s="3">
         <v>500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
+      <c r="AE62" s="3">
+        <v>500</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3300</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6092,25 +6260,28 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>128200</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>115700</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>114400</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-309700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-297400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-287000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-275600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-262400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-250000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-239100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-231300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-223600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-216500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-210100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-204600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-196300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-188200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-180900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-172400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-165100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-155300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-147000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-137500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-130100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-122700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-114200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-100300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-115500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>198500</v>
+      </c>
+      <c r="E76" s="3">
         <v>99500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>99600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>82500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>89600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>95100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>101700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>107500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>109900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>60500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>54500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>67700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-115500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-7400</v>
       </c>
       <c r="W81" s="3">
         <v>-7400</v>
       </c>
       <c r="X81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13500</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-9600</v>
       </c>
       <c r="F89" s="3">
         <v>-9600</v>
       </c>
       <c r="G89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="H89" s="3">
         <v>-8700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,16 +7924,17 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7721,11 +7942,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7734,13 +7955,13 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -7754,26 +7975,26 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7785,22 +8006,25 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,64 +8216,67 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>18000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8070,22 +8300,25 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8151,8 +8385,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,71 +8742,74 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E100" s="3">
         <v>8700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>51500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>55300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>56000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>16100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -8571,31 +8817,34 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>63500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>9800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>10500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8626,8 +8875,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>41900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>58400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -838,8 +841,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -901,8 +904,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E12" s="3">
         <v>10100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1377,12 +1396,12 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1443,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1544,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E17" s="3">
         <v>13900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1847,38 +1880,38 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1889,138 +1922,144 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
       </c>
       <c r="AB20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-500</v>
       </c>
       <c r="AG20" s="3">
         <v>-500</v>
       </c>
       <c r="AH20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-8900</v>
       </c>
       <c r="L21" s="3">
         <v>-8900</v>
       </c>
       <c r="M21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="N21" s="3">
         <v>-8200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,8 +2072,8 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -2052,13 +2091,13 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
@@ -2085,16 +2124,16 @@
         <v>300</v>
       </c>
       <c r="X22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2109,120 +2148,126 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>100</v>
       </c>
       <c r="AH22" s="3">
         <v>100</v>
       </c>
       <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y23" s="3">
         <v>-7400</v>
       </c>
       <c r="Z23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-7400</v>
       </c>
       <c r="AC23" s="3">
         <v>-7400</v>
       </c>
       <c r="AD23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2322,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y26" s="3">
         <v>-7400</v>
       </c>
       <c r="Z26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y27" s="3">
         <v>-7400</v>
       </c>
       <c r="Z27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3059,38 +3128,38 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <v>200</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3101,138 +3170,144 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>500</v>
       </c>
       <c r="AG32" s="3">
         <v>500</v>
       </c>
       <c r="AH32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI32" s="3">
         <v>800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y33" s="3">
         <v>-7400</v>
       </c>
       <c r="Z33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y35" s="3">
         <v>-7400</v>
       </c>
       <c r="Z35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,157 +3698,161 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E41" s="3">
         <v>56900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>41600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>45000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>53300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>44200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>52600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>57300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>63500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>71400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13500</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>169300</v>
+      </c>
+      <c r="E42" s="3">
         <v>138100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>86800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>83900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>56500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>50600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>62900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>80400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>99600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>107900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>59000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>53200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3779,8 +3868,8 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3815,61 +3904,64 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>500</v>
       </c>
       <c r="G43" s="3">
         <v>500</v>
       </c>
       <c r="H43" s="3">
+        <v>500</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>1300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>400</v>
       </c>
       <c r="Q43" s="3">
         <v>400</v>
       </c>
       <c r="R43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
+      <c r="T43" s="3">
+        <v>200</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
@@ -3877,11 +3969,11 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3">
         <v>300</v>
-      </c>
-      <c r="X43" s="3">
-        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
@@ -3890,34 +3982,37 @@
         <v>100</v>
       </c>
       <c r="AA43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB43" s="3">
         <v>600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>300</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>200</v>
       </c>
       <c r="AE43" s="3">
         <v>200</v>
       </c>
       <c r="AF43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG43" s="3">
         <v>100</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3954,8 +4049,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4017,210 +4112,219 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1600</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>191700</v>
+      </c>
+      <c r="E46" s="3">
         <v>198300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>207200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>105600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>109400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>67300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>72100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>76800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>94000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>99200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>114200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>122600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>127300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>79900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>38000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>30700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>38500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>42200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>46300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>55200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>46300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>53800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>59600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>65500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>74600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4257,18 +4361,18 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>1000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4284,8 +4388,8 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4320,49 +4424,52 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
       <c r="F48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1600</v>
       </c>
       <c r="L48" s="3">
         <v>1600</v>
       </c>
       <c r="M48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N48" s="3">
         <v>1700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -4371,13 +4478,13 @@
         <v>100</v>
       </c>
       <c r="S48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T48" s="3">
         <v>200</v>
       </c>
       <c r="U48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V48" s="3">
         <v>300</v>
@@ -4386,7 +4493,7 @@
         <v>300</v>
       </c>
       <c r="X48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y48" s="3">
         <v>400</v>
@@ -4398,7 +4505,7 @@
         <v>400</v>
       </c>
       <c r="AB48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC48" s="3">
         <v>500</v>
@@ -4407,13 +4514,13 @@
         <v>500</v>
       </c>
       <c r="AE48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AF48" s="3">
         <v>100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
+      <c r="AG48" s="3">
+        <v>100</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>4</v>
@@ -4421,8 +4528,11 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4522,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,25 +4840,28 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
@@ -4757,46 +4876,46 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
       <c r="P52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
       </c>
       <c r="S52" s="3">
+        <v>400</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
-      </c>
-      <c r="U52" s="3">
-        <v>400</v>
       </c>
       <c r="V52" s="3">
         <v>400</v>
       </c>
       <c r="W52" s="3">
+        <v>400</v>
+      </c>
+      <c r="X52" s="3">
         <v>500</v>
-      </c>
-      <c r="X52" s="3">
-        <v>300</v>
       </c>
       <c r="Y52" s="3">
         <v>300</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4808,25 +4927,28 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>193400</v>
+      </c>
+      <c r="E54" s="3">
         <v>199400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>110900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>89400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>95900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>101000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>116200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>123000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>128400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>47100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>55900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>47000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>54200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>66000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>75100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15400</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,109 +5230,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5238,10 +5371,10 @@
         <v>300</v>
       </c>
       <c r="N58" s="3">
+        <v>300</v>
+      </c>
+      <c r="O58" s="3">
         <v>7700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>7000</v>
       </c>
       <c r="P58" s="3">
         <v>7000</v>
@@ -5250,23 +5383,23 @@
         <v>7000</v>
       </c>
       <c r="R58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S58" s="3">
         <v>7100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5282,8 +5415,8 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5303,8 +5436,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5341,241 +5477,247 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3900</v>
-      </c>
-      <c r="T59" s="3">
-        <v>3400</v>
       </c>
       <c r="U59" s="3">
         <v>3400</v>
       </c>
       <c r="V59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W59" s="3">
         <v>4000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E60" s="3">
         <v>9000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1900</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>700</v>
       </c>
       <c r="G61" s="3">
         <v>700</v>
       </c>
       <c r="H61" s="3">
+        <v>700</v>
+      </c>
+      <c r="I61" s="3">
         <v>800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>900</v>
       </c>
       <c r="J61" s="3">
         <v>900</v>
       </c>
       <c r="K61" s="3">
+        <v>900</v>
+      </c>
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5592,22 +5734,25 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>1100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5644,8 +5789,8 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5660,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -5672,7 +5817,7 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
@@ -5681,7 +5826,7 @@
         <v>200</v>
       </c>
       <c r="AA62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB62" s="3">
         <v>300</v>
@@ -5690,16 +5835,16 @@
         <v>300</v>
       </c>
       <c r="AD62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE62" s="3">
         <v>800</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>500</v>
       </c>
       <c r="AF62" s="3">
         <v>500</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
+      <c r="AG62" s="3">
+        <v>500</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
@@ -5707,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3300</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6434,25 +6601,28 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>128200</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>115700</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>114400</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-329800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-321500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-309700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-297400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-287000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-275600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-262400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-250000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-239100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-231300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-223600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-216500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-210100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-204600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-196300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-188200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-180900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-172400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-165100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-155300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-147000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-137500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-130100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-122700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-114200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-100300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-115500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>183200</v>
+      </c>
+      <c r="E76" s="3">
         <v>189800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>198500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>99500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>99600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>89600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>95100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>101700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>109900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>60500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>40000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>54500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>60700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>67700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-115500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-7400</v>
       </c>
       <c r="Y81" s="3">
         <v>-7400</v>
       </c>
       <c r="Z81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7503,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13500</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-9600</v>
       </c>
       <c r="H89" s="3">
         <v>-9600</v>
       </c>
       <c r="I89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,22 +8365,23 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -8169,11 +8389,11 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8182,13 +8402,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -8202,26 +8422,26 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8233,22 +8453,25 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,70 +8675,73 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8536,22 +8765,25 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8625,8 +8858,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8688,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,77 +9233,80 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>110400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>51500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>55300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>56000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>16100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -9069,31 +9314,34 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>63500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>9800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>10500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9130,8 +9378,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9193,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-60200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-54000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>41900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>58400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TRVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>TRVI</t>
   </si>
@@ -656,155 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -844,8 +848,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -907,8 +911,11 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,8 +1018,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1399,12 +1419,12 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1465,8 +1485,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E17" s="3">
         <v>10200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1883,38 +1917,38 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1925,141 +1959,147 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
       </c>
       <c r="AC20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-500</v>
       </c>
       <c r="AH20" s="3">
         <v>-500</v>
       </c>
       <c r="AI20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-8900</v>
       </c>
       <c r="M21" s="3">
         <v>-8900</v>
       </c>
       <c r="N21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="O21" s="3">
         <v>-8200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2075,8 +2115,8 @@
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -2094,13 +2134,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>300</v>
@@ -2127,16 +2167,16 @@
         <v>300</v>
       </c>
       <c r="Y22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2151,123 +2191,129 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>100</v>
       </c>
       <c r="AI22" s="3">
         <v>100</v>
       </c>
       <c r="AJ22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z23" s="3">
         <v>-7400</v>
       </c>
       <c r="AA23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-7400</v>
       </c>
       <c r="AD23" s="3">
         <v>-7400</v>
       </c>
       <c r="AE23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,8 +2416,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z26" s="3">
         <v>-7400</v>
       </c>
       <c r="AA26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z27" s="3">
         <v>-7400</v>
       </c>
       <c r="AA27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3131,38 +3201,38 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3173,141 +3243,147 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>500</v>
       </c>
       <c r="AH32" s="3">
         <v>500</v>
       </c>
       <c r="AI32" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z33" s="3">
         <v>-7400</v>
       </c>
       <c r="AA33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z35" s="3">
         <v>-7400</v>
       </c>
       <c r="AA35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,163 +3785,167 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E41" s="3">
         <v>18900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>41600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>45000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>53300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>52600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>57300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>63500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>71400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13500</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E42" s="3">
         <v>169300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>138100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>86800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>73500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>49400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>56500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>50600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>62900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>99600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>107900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>53200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3871,8 +3961,8 @@
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3907,64 +3997,67 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>500</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
       </c>
       <c r="I43" s="3">
+        <v>500</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>400</v>
       </c>
       <c r="R43" s="3">
         <v>400</v>
       </c>
       <c r="S43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
+      <c r="U43" s="3">
+        <v>200</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
@@ -3972,11 +4065,11 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3">
         <v>300</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>100</v>
@@ -3985,34 +4078,37 @@
         <v>100</v>
       </c>
       <c r="AB43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>300</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>200</v>
       </c>
       <c r="AF43" s="3">
         <v>200</v>
       </c>
       <c r="AG43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH43" s="3">
         <v>100</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4052,8 +4148,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4115,216 +4211,225 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1600</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>176100</v>
+      </c>
+      <c r="E46" s="3">
         <v>191700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>198300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>105600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>72100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>87500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>94000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>99200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>114200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>122600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>127300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>79900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>38000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>38500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>42200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>46300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>55200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>46300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>53800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>59600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>65500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>74600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15200</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4364,18 +4469,18 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S47" s="3">
         <v>1000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4391,8 +4496,8 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4427,8 +4532,11 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4436,43 +4544,43 @@
         <v>900</v>
       </c>
       <c r="E48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
       </c>
       <c r="G48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1600</v>
       </c>
       <c r="M48" s="3">
         <v>1600</v>
       </c>
       <c r="N48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>100</v>
       </c>
       <c r="R48" s="3">
         <v>100</v>
@@ -4481,13 +4589,13 @@
         <v>100</v>
       </c>
       <c r="T48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U48" s="3">
         <v>200</v>
       </c>
       <c r="V48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W48" s="3">
         <v>300</v>
@@ -4496,7 +4604,7 @@
         <v>300</v>
       </c>
       <c r="Y48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z48" s="3">
         <v>400</v>
@@ -4508,7 +4616,7 @@
         <v>400</v>
       </c>
       <c r="AC48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD48" s="3">
         <v>500</v>
@@ -4517,13 +4625,13 @@
         <v>500</v>
       </c>
       <c r="AF48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG48" s="3">
         <v>100</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
+      <c r="AH48" s="3">
+        <v>100</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>4</v>
@@ -4531,8 +4639,11 @@
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,28 +4960,31 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -4879,46 +4999,46 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
+        <v>300</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
         <v>900</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
       </c>
       <c r="T52" s="3">
+        <v>400</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>400</v>
       </c>
       <c r="X52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y52" s="3">
         <v>500</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>300</v>
       </c>
       <c r="Z52" s="3">
         <v>300</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4930,25 +5050,28 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E54" s="3">
         <v>193400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>199400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>110900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>89400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>95900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>101000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>116200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>123000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>128400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>81400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>47100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>55900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>47000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>54200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>66000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>75100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15400</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5361,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5374,10 +5508,10 @@
         <v>300</v>
       </c>
       <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
         <v>7700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>7000</v>
       </c>
       <c r="Q58" s="3">
         <v>7000</v>
@@ -5386,23 +5520,23 @@
         <v>7000</v>
       </c>
       <c r="S58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="T58" s="3">
         <v>7100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5418,8 +5552,8 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5439,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5480,175 +5617,181 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3900</v>
-      </c>
-      <c r="U59" s="3">
-        <v>3400</v>
       </c>
       <c r="V59" s="3">
         <v>3400</v>
       </c>
       <c r="W59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X59" s="3">
         <v>4000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1300</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E60" s="3">
         <v>9700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1900</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5656,71 +5799,71 @@
         <v>400</v>
       </c>
       <c r="E61" s="3">
+        <v>400</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>700</v>
       </c>
       <c r="H61" s="3">
         <v>700</v>
       </c>
       <c r="I61" s="3">
+        <v>700</v>
+      </c>
+      <c r="J61" s="3">
         <v>800</v>
-      </c>
-      <c r="J61" s="3">
-        <v>900</v>
       </c>
       <c r="K61" s="3">
         <v>900</v>
       </c>
       <c r="L61" s="3">
+        <v>900</v>
+      </c>
+      <c r="M61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5737,22 +5880,25 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>1100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5792,8 +5938,8 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5808,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -5820,7 +5966,7 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z62" s="3">
         <v>200</v>
@@ -5829,7 +5975,7 @@
         <v>200</v>
       </c>
       <c r="AB62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC62" s="3">
         <v>300</v>
@@ -5838,16 +5984,16 @@
         <v>300</v>
       </c>
       <c r="AE62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF62" s="3">
         <v>800</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>500</v>
       </c>
       <c r="AG62" s="3">
         <v>500</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
+      <c r="AH62" s="3">
+        <v>500</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E66" s="3">
         <v>10200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3300</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6604,25 +6772,28 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>128200</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>115700</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>114400</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-343000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-329800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-321500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-309700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-297400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-287000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-275600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-262400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-250000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-239100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-231300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-223600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-216500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-204600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-196300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-188200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-180900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-172400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-165100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-155300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-147000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-137500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-130100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-122700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-114200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-107700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-100300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-115500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-109500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-102300</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E76" s="3">
         <v>183200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>198500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>99500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>66200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>82500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>95100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>107500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>109900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>40000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>54500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>60700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>67700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-115500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-109500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-102300</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9500</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-7400</v>
       </c>
       <c r="Z81" s="3">
         <v>-7400</v>
       </c>
       <c r="AA81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7798,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7704,8 +7903,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-9600</v>
       </c>
       <c r="I89" s="3">
         <v>-9600</v>
       </c>
       <c r="J89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,25 +8586,26 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -8392,11 +8613,11 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8405,13 +8626,13 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -8425,26 +8646,26 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -8456,22 +8677,25 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,73 +8905,76 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -8768,22 +8998,25 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8861,8 +9095,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,80 +9479,83 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>110400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>51500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>55300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>56000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>16100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -9317,31 +9563,34 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>63500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>9800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>10500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9381,8 +9630,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-60200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>41900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>58400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-4700</v>
       </c>
     </row>
